--- a/templates/RTC_template.xlsx
+++ b/templates/RTC_template.xlsx
@@ -35,8 +35,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="187" formatCode="??.00"/>
+    <numFmt numFmtId="200" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -543,7 +544,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -644,7 +645,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -652,7 +653,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -808,6 +809,22 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="200" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="200" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="200" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="200" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
